--- a/data/numeric/input/data_420/20250901-20250930-对公.xlsx
+++ b/data/numeric/input/data_420/20250901-20250930-对公.xlsx
@@ -501,7 +501,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NG|20250901121641205685485S0310006|0901_1648040677|财付通.</t>
+          <t>NG|20250901121641205685485S0310006|0901_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NG|20250902011747505295628S0110602|0902_1627639995|财付通.</t>
+          <t>NG|20250902011747505295628S0110602|0902_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -610,7 +610,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NG|20250902021646414094517S0210302|0902_1648040677|财付通.</t>
+          <t>NG|20250902021646414094517S0210302|0902_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -645,7 +645,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NG|20250903011748806668727S0111207|0903_1627639995|财付通.</t>
+          <t>NG|20250903011748806668727S0111207|0903_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -680,7 +680,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NG|2025090300113343459813640210000|抖音生活服务商家提现|抖音支付.</t>
+          <t>NG|2025090300113343459813640210000|生活服务平台商家提现|支付平台B.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NG|20250903041743601389064S0310405|0903_1648040677|财付通.</t>
+          <t>NG|20250903041743601389064S0310405|0903_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -750,7 +750,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NG|20250904031647310459612S0200205|0904_1627639995|财付通.</t>
+          <t>NG|20250904031647310459612S0200205|0904_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -785,7 +785,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NG|2025090400117523473173990100000|抖音生活服务商家提现|抖音支付.</t>
+          <t>NG|2025090400117523473173990100000|生活服务平台商家提现|支付平台B.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -820,7 +820,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NG|20250904121649006544384S0311105|0904_1648040677|财付通.</t>
+          <t>NG|20250904121649006544384S0311105|0904_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -855,7 +855,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NG|20250905051943105404446S0111001|0905_1627639995|财付通.</t>
+          <t>NG|20250905051943105404446S0111001|0905_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -890,7 +890,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NG|2025090500110413484157380200000|抖音生活服务商家提现|抖音支付.</t>
+          <t>NG|2025090500110413484157380200000|生活服务平台商家提现|支付平台B.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -925,7 +925,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NG|20250905121741314598985S0310803|0905_1648040677|财付通.</t>
+          <t>NG|20250905121741314598985S0310803|0905_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -960,7 +960,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NG|20250906091649310087175S0300802|0906_1627639995|财付通.</t>
+          <t>NG|20250906091649310087175S0300802|0906_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -995,7 +995,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NG|2025090600111173659152230300000|抖音生活服务商家提现|抖音支付.</t>
+          <t>NG|2025090600111173659152230300000|生活服务平台商家提现|支付平台B.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NG|20250906021742001494217S0211104|0906_1648040677|财付通.</t>
+          <t>NG|20250906021742001494217S0211104|0906_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NG|20250907031741111944614S0200104|0907_1627639995|财付通.</t>
+          <t>NG|20250907031741111944614S0200104|0907_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1100,7 +1100,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NG|2025090700119463478979250100000|抖音生活服务商家提现|抖音支付.</t>
+          <t>NG|2025090700119463478979250100000|生活服务平台商家提现|支付平台B.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1135,7 +1135,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NG|20250907041748701880163S0310204|0907_1648040677|财付通.</t>
+          <t>NG|20250907041748701880163S0310204|0907_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NG|20250908031742315278014S0200805|0908_1627639995|财付通.</t>
+          <t>NG|20250908031742315278014S0200805|0908_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>银联，商户113513070110086转入，手续费0.65元.</t>
+          <t>银联，商户商户编号XXX转入，手续费0.65元.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NG|20250908101742617894532S0200908|0908_1648040677|财付通.</t>
+          <t>NG|20250908101742617894532S0200908|0908_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NG|20250909091743404390575S0300503|0909_1627639995|财付通.</t>
+          <t>NG|20250909091743404390575S0300503|0909_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1388,7 +1388,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NG|20250909121841512872686S0311109|0909_1648040677|财付通.</t>
+          <t>NG|20250909121841512872686S0311109|0909_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1423,7 +1423,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NG|20250910011847806642428S0110003|0910_1627639995|财付通.</t>
+          <t>NG|20250910011847806642428S0110003|0910_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1497,7 +1497,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NG|20250910121843914695784S0310602|0910_1648040677|财付通.</t>
+          <t>NG|20250910121843914695784S0310602|0910_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1532,7 +1532,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NG|20250911052048904454645S0111006|0911_1627639995|财付通.</t>
+          <t>NG|20250911052048904454645S0111006|0911_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1606,7 +1606,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NG|20250912052141208516548S0110201|0912_1627639995|财付通.</t>
+          <t>NG|20250912052141208516548S0110201|0912_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1680,7 +1680,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NG|20250912041844814699261S0311401|0912_1648040677|财付通.</t>
+          <t>NG|20250912041844814699261S0311401|0912_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1715,7 +1715,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NG|20250913052143610182648S0110308|0913_1627639995|财付通.</t>
+          <t>NG|20250913052143610182648S0110308|0913_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1789,7 +1789,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NG|20250913121941813751885S0310505|0913_1648040677|财付通.</t>
+          <t>NG|20250913121941813751885S0310505|0913_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1859,7 +1859,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NG|20250914091840004463974S0301305|0914_1627639995|财付通.</t>
+          <t>NG|20250914091840004463974S0301305|0914_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1933,7 +1933,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NG|20250914041847315632264S0310305|0914_1648040677|财付通.</t>
+          <t>NG|20250914041847315632264S0310305|0914_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1968,7 +1968,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>NG|20250915052148317259448S0111406|0915_1627639995|财付通.</t>
+          <t>NG|20250915052148317259448S0111406|0915_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2042,7 +2042,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NG|20250915121947711520083S0311407|0915_1648040677|财付通.</t>
+          <t>NG|20250915121947711520083S0311407|0915_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2077,7 +2077,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NG|20250916011945408096625S0110507|0916_1627639995|财付通.</t>
+          <t>NG|20250916011945408096625S0110507|0916_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2143,7 +2143,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>付4786账户本金33651.0日志号1942861019手续费（050273）优惠10..</t>
+          <t>付内部账户X本金33651.0日志号1942861019手续费（费用代码A）优惠10..</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2209,7 +2209,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>付4786账户本金11800.0日志号1802877004手续费（050273）优惠10..</t>
+          <t>付内部账户X本金11800.0日志号1802877004手续费（费用代码A）优惠10..</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>供应商-景田矿泉水.</t>
+          <t>供应商-供应商A.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2314,7 +2314,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>付4786账户本金1920.0日志号1944648929手续费（050273）优惠10.0.</t>
+          <t>付内部账户X本金1920.0日志号1944648929手续费（费用代码A）优惠10.0.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2349,7 +2349,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NG|20250916101843207579134S0200500|0916_1648040677|财付通.</t>
+          <t>NG|20250916101843207579134S0200500|0916_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2384,7 +2384,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NG|20250917052244307012448S0110700|0917_1627639995|财付通.</t>
+          <t>NG|20250917052244307012448S0110700|0917_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2458,7 +2458,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NG|20250917021845713701615S0211408|0917_1648040677|财付通.</t>
+          <t>NG|20250917021845713701615S0211408|0917_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2493,7 +2493,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NG|20250918031845513002614S0201004|0918_1627639995|财付通.</t>
+          <t>NG|20250918031845513002614S0201004|0918_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2567,7 +2567,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>NG|20250918021847501689316S0211405|0918_1648040677|财付通.</t>
+          <t>NG|20250918021847501689316S0211405|0918_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>NG|20250919011949105514926S0110106|0919_1627639995|财付通.</t>
+          <t>NG|20250919011949105514926S0110106|0919_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2676,7 +2676,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>NG|20250919021848705189416S0210008|0919_1648040677|财付通.</t>
+          <t>NG|20250919021848705189416S0210008|0919_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2711,7 +2711,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NG|20250920031848504311243S0101403|0920_1627639995|财付通.</t>
+          <t>NG|20250920031848504311243S0101403|0920_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2785,7 +2785,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>NG|20250920101848015719124S0100206|0920_1648040677|财付通.</t>
+          <t>NG|20250920101848015719124S0100206|0920_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2847,7 +2847,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NG|20250921052343920971048S0111102|0921_1627639995|财付通.</t>
+          <t>NG|20250921052343920971048S0111102|0921_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -2921,7 +2921,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NG|20250921021941010129918S0210708|0921_1648040677|财付通.</t>
+          <t>NG|20250921021941010129918S0210708|0921_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -2956,7 +2956,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>NG|20250922052347505234446S0110108|0922_1627639995|财付通.</t>
+          <t>NG|20250922052347505234446S0110108|0922_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3030,7 +3030,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>NG|20250922021942506573218S0211305|0922_1648040677|财付通.</t>
+          <t>NG|20250922021942506573218S0211305|0922_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3065,7 +3065,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>NG|20250923012044209226426S0111101|0923_1627639995|财付通.</t>
+          <t>NG|20250923012044209226426S0111101|0923_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3131,7 +3131,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>付4786账户本金10750.0日志号1872622031手续费（050273）优惠10..</t>
+          <t>付内部账户X本金10750.0日志号1872622031手续费（费用代码A）优惠10..</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3197,7 +3197,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>付4786账户本金26000.0日志号1592617338手续费（050268）优惠10..</t>
+          <t>付内部账户X本金26000.0日志号1592617338手续费（费用代码B）优惠10..</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3271,7 +3271,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>NG|20250923021944001733217S0210000|0923_1648040677|财付通.</t>
+          <t>NG|20250923021944001733217S0210000|0923_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3345,7 +3345,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>NG|2025092465502309300586090100407|支付宝转账;支付宝转账|支付宝.</t>
+          <t>NG|2025092465502309300586090100407|支付平台C转账;支付平台C转账|支付平台C.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3380,7 +3380,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>NG|20250924012045605550827S0110203|0924_1627639995|财付通.</t>
+          <t>NG|20250924012045605550827S0110203|0924_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3454,7 +3454,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>NG|20250925051544713732546S0110203|0925_1627639995|财付通.</t>
+          <t>NG|20250925051544713732546S0110203|0925_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3528,7 +3528,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>NG|20250925042041417119164S0310306|0925_1648040677|财付通.</t>
+          <t>NG|20250925042041417119164S0310306|0925_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3563,7 +3563,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>NG|20250926031946305110412S0200009|0926_1627639995|财付通.</t>
+          <t>NG|20250926031946305110412S0200009|0926_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3637,7 +3637,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>NG|20250926101946103677831S0200808|0926_1648040677|财付通.</t>
+          <t>NG|20250926101946103677831S0200808|0926_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -3672,7 +3672,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>NG|20250927012048913218128S0110902|0927_1627639995|财付通.</t>
+          <t>NG|20250927012048913218128S0110902|0927_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -3746,7 +3746,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>NG|20250927042044404543862S0310606|0927_1648040677|财付通.</t>
+          <t>NG|20250927042044404543862S0310606|0927_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -3781,7 +3781,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>NG|20250928031949004676113S0200608|0928_1627639995|财付通.</t>
+          <t>NG|20250928031949004676113S0200608|0928_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -3855,7 +3855,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>NG|20250928042045510268361S0311207|0928_1648040677|财付通.</t>
+          <t>NG|20250928042045510268361S0311207|0928_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>NG|20250929051645307517147S0110702|0929_1627639995|财付通.</t>
+          <t>NG|20250929051645307517147S0110702|0929_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -3964,7 +3964,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>NG|20250929122343715300983S0311102|0929_1648040677|财付通.</t>
+          <t>NG|20250929122343715300983S0311102|0929_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -3999,7 +3999,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>NG|20250930012143106109727S0111006|0930_1627639995|财付通.</t>
+          <t>NG|20250930012143106109727S0111006|0930_1627639995|支付平台A.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>抖音生活服务商家提现.</t>
+          <t>生活服务平台商家提现.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4073,7 +4073,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>NG|20250930122347202256886S0310708|0930_1648040677|财付通.</t>
+          <t>NG|20250930122347202256886S0310708|0930_1648040677|支付平台A.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4301,13 +4301,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8A4DFB0-90F7-4443-87FD-0B8F5BF8D888}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA655E0D-D791-46E3-AEC9-E4C2D1B117F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E1568C8-5AB8-4151-8027-CB39F660AA22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB86EF0-A880-4654-966A-9EE84C06CFDD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C4EF0AA-C829-4F7F-AE87-2E4E66D37504}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C52F0DA-0716-4966-ACBB-FFF01FFB322B}"/>
 </file>